--- a/output/2026-09-02_01_Italia_Marche_Metalworking_Lavorazioni_Metalliche.xlsx
+++ b/output/2026-09-02_01_Italia_Marche_Metalworking_Lavorazioni_Metalliche.xlsx
@@ -506,7 +506,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Esistenza e telefono confermati via ricerca indipendente (Confapi Pesaro Urbino, PagineBianche). Email fornita ha dominio diverso dal sito (uniair.it vs uniairimpiantiaspirazione.eu) - non riscontrata autonomamente, da verificare umanamente</t>
+          <t>Esistenza e telefono confermati via ricerca indipendente (Confapi Pesaro Urbino, PagineBianche). Email fornita ha dominio diverso dal sito (uniair.it vs uniairimpiantiaspirazione.eu) - non riscontrata autonomamente, da verificare umanamente [DUPLICATO — vedi anche: 2026-09-01_21_Italia_Marche_Impiantistica_aspirazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -541,10 +541,9 @@
           <t>0721 499043</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Impianti di aspirazione e filtrazione industriale, banchi aspiranti, aspirazione trucioli e fumi di saldatura dal 1981. Esistenza e telefono confermati (PagineBianche, Virgilio Aziende)</t>
+          <t>Impianti di aspirazione e filtrazione industriale, banchi aspiranti, aspirazione trucioli e fumi di saldatura dal 1981. Esistenza e telefono confermati (PagineBianche, Virgilio Aziende) [DUPLICATO — vedi anche: 2026-09-01_19_Italia_Marche_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -586,7 +585,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Impianti di aspirazione e filtrazione industriale (polveri, trucioli, nebbie oleose) dal 1974. Esistenza, indirizzo e telefono confermati indipendentemente</t>
+          <t>Impianti di aspirazione e filtrazione industriale (polveri, trucioli, nebbie oleose) dal 1974. Esistenza, indirizzo e telefono confermati indipendentemente [DUPLICATO — vedi anche: 2026-09-01_19_Italia_Marche_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -601,7 +600,6 @@
           <t>Nuova Co.Im.A. S.r.l.</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>Fano (PU) - Marche</t>
@@ -617,7 +615,6 @@
           <t>0721 855401</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>Impianti di aspirazione industriale. Esistenza, indirizzo e telefono confermati (Misterimprese, PagineBianche, Impresa Italia). Nome simile a CO.IM.AS. ma azienda distinta (P.IVA diversa, indirizzo diverso) - non e' un duplicato</t>
@@ -655,10 +652,9 @@
           <t>0721 476657</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Progettazione, produzione e installazione impianti di aspirazione fumo e polveri dal 1984. Esistenza, indirizzo operativo e telefono confermati (Ufficiocamerale, Europages)</t>
+          <t>Progettazione, produzione e installazione impianti di aspirazione fumo e polveri dal 1984. Esistenza, indirizzo operativo e telefono confermati (Ufficiocamerale, Europages) [DUPLICATO — vedi anche: 2026-09-01_19_Italia_Marche_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -673,7 +669,6 @@
           <t>Pieri Aertecnica di Pieri Roberto</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>Pesaro (PU) - Marche</t>
@@ -689,7 +684,6 @@
           <t>347 8586244</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>Impianti di aspirazione. Esistenza e telefono confermati (Virgilio Aziende, PagineBianche, PagineGialle, Reteimprese). Ditta individuale di piccole dimensioni, nessun sito web/email - valutare idoneita' come partner distributivo</t>
@@ -734,7 +728,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Progettazione/produzione/installazione/manutenzione canalizzazioni e impianti di aspirazione industriale. Esistenza e telefono confermati (PagineBianche, Cylex). ATTENZIONE: sede legale fuori regione Marche - incluso con nota esplicativa, valutare se rientra nel perimetro richiesto</t>
+          <t>Progettazione/produzione/installazione/manutenzione canalizzazioni e impianti di aspirazione industriale. Esistenza e telefono confermati (PagineBianche, Cylex). ATTENZIONE: sede legale fuori regione Marche - incluso con nota esplicativa, valutare se rientra nel perimetro richiesto [DUPLICATO — vedi anche: 2026-08-31_16_Italia_Emilia_Romagna_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
